--- a/brand_contacts.xlsx
+++ b/brand_contacts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\33543\Desktop\ML\Group\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF62DD3-F1A6-4947-A0F8-431ED8B7F0CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D84F81F-BFC8-4645-BD0F-8FB17D9AB326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,9 +36,6 @@
     <t>uceict8@ucl.ac.uk</t>
   </si>
   <si>
-    <t>amandatian448@gmail.com</t>
-  </si>
-  <si>
     <t>contact_name</t>
   </si>
   <si>
@@ -79,6 +76,9 @@
   </si>
   <si>
     <t>gaozihan0405@gmail.com</t>
+  </si>
+  <si>
+    <t>975698130@qq.com</t>
   </si>
 </sst>
 </file>
@@ -407,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.26953125" bestFit="1" customWidth="1"/>
@@ -415,79 +415,80 @@
     <col min="3" max="3" width="24.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C3" r:id="rId1" xr:uid="{D5175B89-7C78-4180-B888-D9E1090C705F}"/>
     <hyperlink ref="C2" r:id="rId2" xr:uid="{1DE56AB7-3683-47BA-B6D5-D40903807684}"/>
-    <hyperlink ref="C4" r:id="rId3" xr:uid="{89626107-9884-4E8B-9F32-A719F2DDCDA5}"/>
-    <hyperlink ref="C5" r:id="rId4" xr:uid="{DCBBF667-837C-42A5-BE77-63983AFFC388}"/>
-    <hyperlink ref="C6" r:id="rId5" xr:uid="{6BB994A4-21B3-412A-ABDD-017220B6CEF1}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{DCBBF667-837C-42A5-BE77-63983AFFC388}"/>
+    <hyperlink ref="C6" r:id="rId4" xr:uid="{6BB994A4-21B3-412A-ABDD-017220B6CEF1}"/>
+    <hyperlink ref="C4" r:id="rId5" xr:uid="{73489D44-4E7E-47DC-ADB0-DF6861621BA9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/brand_contacts.xlsx
+++ b/brand_contacts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\33543\Desktop\ML\Group\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D84F81F-BFC8-4645-BD0F-8FB17D9AB326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E6A2B7-4E79-4201-BCD8-23EB67CFE707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>ucei749@ucl.ac.uk</t>
   </si>
@@ -48,9 +48,6 @@
     <t>Cheng Tian</t>
   </si>
   <si>
-    <t>Amanda</t>
-  </si>
-  <si>
     <t>brand</t>
   </si>
   <si>
@@ -78,7 +75,7 @@
     <t>gaozihan0405@gmail.com</t>
   </si>
   <si>
-    <t>975698130@qq.com</t>
+    <t>18761855941@163.com</t>
   </si>
 </sst>
 </file>
@@ -417,7 +414,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" t="s">
         <v>3</v>
@@ -428,7 +425,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
@@ -439,7 +436,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -453,33 +450,33 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
